--- a/बजेट माग estimate/thekka/बुढिचौर लिफ्ट/बुढिचौर लिफ्ट y - sir.xlsx
+++ b/बजेट माग estimate/thekka/बुढिचौर लिफ्ट/बुढिचौर लिफ्ट y - sir.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FD3AB03-6253-4D88-8F4D-FD46A70D618F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1B7EB8-D95C-4E9C-8315-7006FAB7EBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$100</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$80</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -118,24 +118,9 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Budget allocated</t>
-  </si>
-  <si>
-    <t>Municipal payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingencies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintanince </t>
-  </si>
-  <si>
     <t>F.Y.: 2082/2083</t>
   </si>
   <si>
-    <t>User contribution</t>
-  </si>
-  <si>
     <t>Length (m)</t>
   </si>
   <si>
@@ -160,9 +145,6 @@
     <t>Location:- Shankharapur Municipality 1</t>
   </si>
   <si>
-    <t>-13% VAT for material</t>
-  </si>
-  <si>
     <t>-for pipe laying</t>
   </si>
   <si>
@@ -190,18 +172,9 @@
     <t>-for stand taps</t>
   </si>
   <si>
-    <t>-13% VAT for sand</t>
-  </si>
-  <si>
     <t>Plain cement concrete (1:2:4)</t>
   </si>
   <si>
-    <t>-13% VAT for cement</t>
-  </si>
-  <si>
-    <t>-13% VAT for aggregate</t>
-  </si>
-  <si>
     <t>sqm</t>
   </si>
   <si>
@@ -238,9 +211,6 @@
     <t>20mm GI pipe threaded-Medium class</t>
   </si>
   <si>
-    <t>-13% VAT</t>
-  </si>
-  <si>
     <t>thickness</t>
   </si>
   <si>
@@ -251,9 +221,6 @@
   </si>
   <si>
     <t>Flat brick  soling</t>
-  </si>
-  <si>
-    <t>-13% VAT for brick</t>
   </si>
   <si>
     <t>Chimney made Brick work in 1:6 cement mortar</t>
@@ -513,7 +480,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -633,6 +600,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -654,21 +627,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1196,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y100"/>
+  <dimension ref="A1:Y80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
@@ -1219,113 +1177,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
     </row>
     <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
     </row>
     <row r="6" spans="1:25" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="A6" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="H6" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="A7" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="H7" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -1371,10 +1329,10 @@
     </row>
     <row r="9" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7"/>
@@ -1391,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="24"/>
@@ -1413,7 +1371,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
       <c r="B11" s="19" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C11" s="20">
         <v>3</v>
@@ -1450,14 +1408,15 @@
         <v>1.2700799999999999</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I12" s="2">
-        <v>963.05</v>
+        <f>1.15*963.05</f>
+        <v>1107.5074999999999</v>
       </c>
       <c r="J12" s="17">
         <f>G12*I12</f>
-        <v>1223.1505439999999</v>
+        <v>1406.6231255999999</v>
       </c>
       <c r="K12" s="15"/>
     </row>
@@ -1479,7 +1438,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -1494,7 +1453,7 @@
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="19" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C15" s="20">
         <v>3</v>
@@ -1529,22 +1488,21 @@
         <v>8.4672000000000001</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I16" s="2">
-        <v>1014.15</v>
+        <f>1.15*1014.15</f>
+        <v>1166.2724999999998</v>
       </c>
       <c r="J16" s="17">
         <f>G16*I16</f>
-        <v>8587.0108799999998</v>
+        <v>9875.0625119999986</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="18"/>
-      <c r="B17" s="19" t="s">
-        <v>66</v>
-      </c>
+      <c r="B17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
@@ -1552,16 +1510,15 @@
       <c r="G17" s="20"/>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
-      <c r="J17" s="17">
-        <f>0.13*G16*636.09</f>
-        <v>700.16716224000004</v>
-      </c>
+      <c r="J17" s="20"/>
       <c r="K17" s="20"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19" t="s">
-        <v>45</v>
+      <c r="A18" s="18">
+        <v>3</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>39</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -1570,168 +1527,203 @@
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
-      <c r="J18" s="17">
-        <f>0.13*G16*222.31</f>
-        <v>244.70462015999999</v>
-      </c>
+      <c r="J18" s="20"/>
       <c r="K18" s="20"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="18"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="B19" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="20">
+        <f>C15</f>
+        <v>3</v>
+      </c>
+      <c r="D19" s="21">
+        <v>1.68</v>
+      </c>
+      <c r="E19" s="21">
+        <v>1.68</v>
+      </c>
+      <c r="F19" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="21">
+        <f>PRODUCT(C19:F19)</f>
+        <v>0.84672000000000003</v>
+      </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
       <c r="K19" s="20"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="18">
-        <v>3</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="2">
+        <f>SUM(G19)</f>
+        <v>0.84672000000000003</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="2">
+        <f>1.15*13343.7</f>
+        <v>15345.254999999999</v>
+      </c>
+      <c r="J20" s="17">
+        <f>G20*I20</f>
+        <v>12993.1343136</v>
+      </c>
+      <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
-      <c r="B21" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="20">
-        <f>C15</f>
-        <v>3</v>
-      </c>
-      <c r="D21" s="21">
-        <v>1.68</v>
-      </c>
-      <c r="E21" s="21">
-        <v>1.68</v>
-      </c>
-      <c r="F21" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="G21" s="21">
-        <f>PRODUCT(C21:F21)</f>
-        <v>0.84672000000000003</v>
-      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="2">
-        <f>SUM(G21)</f>
-        <v>0.84672000000000003</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I22" s="2">
-        <v>13343.7</v>
-      </c>
-      <c r="J22" s="17">
-        <f>G22*I22</f>
-        <v>11298.377664000001</v>
-      </c>
-      <c r="K22" s="15"/>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
+        <v>4</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+        <v>41</v>
+      </c>
+      <c r="C23" s="20">
+        <f>C15*2</f>
+        <v>6</v>
+      </c>
+      <c r="D23" s="21">
+        <v>1.2</v>
+      </c>
+      <c r="E23" s="21">
+        <v>0.23</v>
+      </c>
+      <c r="F23" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="G23" s="21">
+        <f>PRODUCT(C23:F23)</f>
+        <v>0.99359999999999993</v>
+      </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
-      <c r="J23" s="17">
-        <f>0.13*G22*1413.27</f>
-        <v>155.563716672</v>
-      </c>
+      <c r="J23" s="20"/>
       <c r="K23" s="20"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+        <v>42</v>
+      </c>
+      <c r="C24" s="20">
+        <f>C15</f>
+        <v>3</v>
+      </c>
+      <c r="D24" s="21">
+        <v>1.32</v>
+      </c>
+      <c r="E24" s="21">
+        <v>0.23</v>
+      </c>
+      <c r="F24" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="G24" s="21">
+        <f>PRODUCT(C24:F24)</f>
+        <v>0.54647999999999997</v>
+      </c>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
-      <c r="J24" s="17">
-        <f>0.13*G22*4096</f>
-        <v>450.86146560000003</v>
-      </c>
+      <c r="J24" s="20"/>
       <c r="K24" s="20"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="18"/>
-      <c r="B25" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
+      <c r="B25" s="19" t="str">
+        <f>B19</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C25" s="20">
+        <f>C15</f>
+        <v>3</v>
+      </c>
+      <c r="D25" s="21">
+        <v>0.35</v>
+      </c>
+      <c r="E25" s="21">
+        <v>0.23</v>
+      </c>
+      <c r="F25" s="21">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="21">
+        <f>PRODUCT(C25:F25)</f>
+        <v>0.28979999999999995</v>
+      </c>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
-      <c r="J25" s="17">
-        <f>0.13*G22*(368.76+737.51+1743.21)</f>
-        <v>313.65252172800001</v>
-      </c>
+      <c r="J25" s="20"/>
       <c r="K25" s="20"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-    </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
-        <v>4</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>67</v>
-      </c>
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="2">
+        <f>SUM(G23:G25)</f>
+        <v>1.8298799999999997</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="2">
+        <f>1.15*12225.55</f>
+        <v>14059.382499999998</v>
+      </c>
+      <c r="J26" s="17">
+        <f>G26*I26</f>
+        <v>25726.982849099993</v>
+      </c>
+      <c r="K26" s="15"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="18"/>
+      <c r="B27" s="20"/>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
@@ -1743,27 +1735,17 @@
       <c r="K27" s="20"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="20">
-        <f>C15*2</f>
-        <v>6</v>
-      </c>
-      <c r="D28" s="21">
-        <v>1.2</v>
-      </c>
-      <c r="E28" s="21">
-        <v>0.23</v>
-      </c>
-      <c r="F28" s="21">
-        <v>0.6</v>
-      </c>
-      <c r="G28" s="21">
-        <f>PRODUCT(C28:F28)</f>
-        <v>0.99359999999999993</v>
-      </c>
+      <c r="A28" s="18">
+        <v>5</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
@@ -1771,25 +1753,26 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
-      <c r="B29" s="19" t="s">
-        <v>51</v>
+      <c r="B29" s="19" t="str">
+        <f>B23</f>
+        <v>-for wing walls of stand tap</v>
       </c>
       <c r="C29" s="20">
-        <f>C15</f>
-        <v>3</v>
+        <f>C15*4</f>
+        <v>12</v>
       </c>
       <c r="D29" s="21">
-        <v>1.32</v>
-      </c>
-      <c r="E29" s="21">
-        <v>0.23</v>
-      </c>
+        <f>D23</f>
+        <v>1.2</v>
+      </c>
+      <c r="E29" s="21"/>
       <c r="F29" s="21">
+        <f>F23</f>
         <v>0.6</v>
       </c>
       <c r="G29" s="21">
         <f>PRODUCT(C29:F29)</f>
-        <v>0.54647999999999997</v>
+        <v>8.6399999999999988</v>
       </c>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
@@ -1799,97 +1782,111 @@
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="18"/>
       <c r="B30" s="19" t="str">
-        <f>B21</f>
-        <v>-for stand tap</v>
+        <f>B24</f>
+        <v>-for side wall of stand tap</v>
       </c>
       <c r="C30" s="20">
         <f>C15</f>
         <v>3</v>
       </c>
       <c r="D30" s="21">
-        <v>0.35</v>
-      </c>
-      <c r="E30" s="21">
-        <v>0.23</v>
-      </c>
+        <f>D24</f>
+        <v>1.32</v>
+      </c>
+      <c r="E30" s="21"/>
       <c r="F30" s="21">
-        <v>1.2</v>
+        <f>F24</f>
+        <v>0.6</v>
       </c>
       <c r="G30" s="21">
         <f>PRODUCT(C30:F30)</f>
-        <v>0.28979999999999995</v>
+        <v>2.3759999999999999</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
       <c r="J30" s="20"/>
       <c r="K30" s="20"/>
     </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="2">
-        <f>SUM(G28:G30)</f>
-        <v>1.8298799999999997</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I31" s="2">
-        <v>12225.55</v>
-      </c>
-      <c r="J31" s="17">
-        <f>G31*I31</f>
-        <v>22371.289433999995</v>
-      </c>
-      <c r="K31" s="15"/>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="18"/>
+      <c r="B31" s="19" t="str">
+        <f>B25</f>
+        <v>-for stand tap</v>
+      </c>
+      <c r="C31" s="20">
+        <f>C15</f>
+        <v>3</v>
+      </c>
+      <c r="D31" s="21">
+        <f>D25</f>
+        <v>0.35</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21">
+        <f>F25</f>
+        <v>1.2</v>
+      </c>
+      <c r="G31" s="21">
+        <f>PRODUCT(C31:F31)</f>
+        <v>1.2599999999999998</v>
+      </c>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
-      <c r="B32" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="20">
+        <f>C31</f>
+        <v>3</v>
+      </c>
+      <c r="D32" s="21">
+        <v>0.46</v>
+      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="G32" s="21">
+        <f>PRODUCT(C32:F32)</f>
+        <v>0.82800000000000007</v>
+      </c>
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
-      <c r="J32" s="17">
-        <f>0.13*G31*8481.2</f>
-        <v>2017.54517328</v>
-      </c>
+      <c r="J32" s="20"/>
       <c r="K32" s="20"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
+    <row r="33" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="2">
+        <f>SUM(G29:G32)</f>
+        <v>13.103999999999997</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="2">
+        <f>1.15*49954.32/100</f>
+        <v>574.47467999999992</v>
+      </c>
       <c r="J33" s="17">
-        <f>0.13*G31*896</f>
-        <v>213.14442239999997</v>
-      </c>
-      <c r="K33" s="20"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <f>G33*I33</f>
+        <v>7527.9162067199977</v>
+      </c>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
-      <c r="B34" s="19" t="s">
-        <v>45</v>
-      </c>
+      <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
       <c r="E34" s="20"/>
@@ -1897,15 +1894,16 @@
       <c r="G34" s="20"/>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
-      <c r="J34" s="17">
-        <f>0.13*G31*952.76</f>
-        <v>226.64674094399996</v>
-      </c>
+      <c r="J34" s="20"/>
       <c r="K34" s="20"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
-      <c r="B35" s="20"/>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A35" s="18">
+        <v>6</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>49</v>
+      </c>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
@@ -1916,131 +1914,141 @@
       <c r="J35" s="20"/>
       <c r="K35" s="20"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="18">
-        <v>5</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A36" s="18"/>
+      <c r="B36" s="19" t="str">
+        <f t="shared" ref="B36:D38" si="0">B29</f>
+        <v>-for wing walls of stand tap</v>
+      </c>
+      <c r="C36" s="20">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="D36" s="21">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21">
+        <f>F29</f>
+        <v>0.6</v>
+      </c>
+      <c r="G36" s="21">
+        <f>PRODUCT(C36:F36)</f>
+        <v>8.6399999999999988</v>
+      </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
       <c r="K36" s="20"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="18"/>
       <c r="B37" s="19" t="str">
-        <f>B28</f>
-        <v>-for wing walls of stand tap</v>
+        <f t="shared" si="0"/>
+        <v>-for side wall of stand tap</v>
       </c>
       <c r="C37" s="20">
-        <f>C15*4</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="D37" s="21">
-        <f>D28</f>
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>1.32</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21">
-        <f>F28</f>
+        <f>F30</f>
         <v>0.6</v>
       </c>
       <c r="G37" s="21">
         <f>PRODUCT(C37:F37)</f>
-        <v>8.6399999999999988</v>
+        <v>2.3759999999999999</v>
       </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
       <c r="K37" s="20"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="18"/>
       <c r="B38" s="19" t="str">
-        <f>B29</f>
-        <v>-for side wall of stand tap</v>
+        <f t="shared" si="0"/>
+        <v>-for stand tap</v>
       </c>
       <c r="C38" s="20">
-        <f>C15</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D38" s="21">
-        <f>D29</f>
-        <v>1.32</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21">
-        <f>F29</f>
-        <v>0.6</v>
+        <f>F31</f>
+        <v>1.2</v>
       </c>
       <c r="G38" s="21">
         <f>PRODUCT(C38:F38)</f>
-        <v>2.3759999999999999</v>
+        <v>1.2599999999999998</v>
       </c>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
       <c r="K38" s="20"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="18"/>
-      <c r="B39" s="19" t="str">
-        <f>B30</f>
-        <v>-for stand tap</v>
-      </c>
+      <c r="B39" s="19"/>
       <c r="C39" s="20">
-        <f>C15</f>
+        <f>C32</f>
         <v>3</v>
       </c>
       <c r="D39" s="21">
-        <f>D30</f>
-        <v>0.35</v>
+        <f>D32</f>
+        <v>0.46</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21">
-        <f>F30</f>
-        <v>1.2</v>
+        <f>F32</f>
+        <v>0.6</v>
       </c>
       <c r="G39" s="21">
         <f>PRODUCT(C39:F39)</f>
-        <v>1.2599999999999998</v>
+        <v>0.82800000000000007</v>
       </c>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
       <c r="K39" s="20"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="18"/>
-      <c r="B40" s="19"/>
+      <c r="B40" s="19" t="s">
+        <v>50</v>
+      </c>
       <c r="C40" s="20">
-        <f>C39</f>
+        <f>C15</f>
         <v>3</v>
       </c>
       <c r="D40" s="21">
-        <v>0.46</v>
-      </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21">
-        <v>0.6</v>
-      </c>
+        <v>1.68</v>
+      </c>
+      <c r="E40" s="21">
+        <v>1.68</v>
+      </c>
+      <c r="F40" s="21"/>
       <c r="G40" s="21">
         <f>PRODUCT(C40:F40)</f>
-        <v>0.82800000000000007</v>
+        <v>8.4672000000000001</v>
       </c>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
       <c r="K40" s="20"/>
     </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="13" t="s">
         <v>16</v>
@@ -2050,27 +2058,25 @@
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
       <c r="G41" s="2">
-        <f>SUM(G37:G40)</f>
-        <v>13.103999999999997</v>
+        <f>SUM(G36:G40)</f>
+        <v>21.571199999999997</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I41" s="2">
-        <f>49954.32/100</f>
-        <v>499.54320000000001</v>
+        <f>1.15*28609.6/100</f>
+        <v>329.01039999999995</v>
       </c>
       <c r="J41" s="17">
         <f>G41*I41</f>
-        <v>6546.0140927999992</v>
+        <v>7097.1491404799981</v>
       </c>
       <c r="K41" s="15"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="18"/>
-      <c r="B42" s="19" t="s">
-        <v>45</v>
-      </c>
+      <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
@@ -2078,16 +2084,15 @@
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
-      <c r="J42" s="17">
-        <f>0.13*G41*7463.32/100</f>
-        <v>127.13914886399998</v>
-      </c>
+      <c r="J42" s="20"/>
       <c r="K42" s="20"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="18"/>
-      <c r="B43" s="19" t="s">
-        <v>47</v>
+    <row r="43" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="18">
+        <v>7</v>
+      </c>
+      <c r="B43" s="41" t="s">
+        <v>51</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
@@ -2096,207 +2101,213 @@
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
       <c r="I43" s="20"/>
-      <c r="J43" s="17">
-        <f>0.13*G41*7296/100</f>
-        <v>124.28881919999998</v>
-      </c>
+      <c r="J43" s="20"/>
       <c r="K43" s="20"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="10"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="10"/>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="18"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
+      <c r="B44" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="20">
+        <f>C15</f>
+        <v>3</v>
+      </c>
+      <c r="D44" s="21">
+        <v>1.2</v>
+      </c>
       <c r="E44" s="20"/>
       <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
+      <c r="G44" s="21">
+        <f>PRODUCT(C44:F44)</f>
+        <v>3.5999999999999996</v>
+      </c>
       <c r="H44" s="20"/>
       <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
+      <c r="J44" s="17"/>
       <c r="K44" s="20"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="18">
-        <v>6</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="14"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="43">
+        <f>SUM(G44:G44)</f>
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="2">
+        <v>248</v>
+      </c>
+      <c r="J45" s="43">
+        <f>G45*I45</f>
+        <v>892.8</v>
+      </c>
+      <c r="K45" s="15"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="18"/>
-      <c r="B46" s="19" t="str">
-        <f>B37</f>
-        <v>-for wing walls of stand tap</v>
-      </c>
-      <c r="C46" s="20">
-        <f>C37</f>
-        <v>12</v>
-      </c>
-      <c r="D46" s="21">
-        <f>D37</f>
-        <v>1.2</v>
-      </c>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21">
-        <f>F37</f>
-        <v>0.6</v>
-      </c>
-      <c r="G46" s="21">
-        <f>PRODUCT(C46:F46)</f>
-        <v>8.6399999999999988</v>
-      </c>
+      <c r="B46" s="41"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
       <c r="H46" s="20"/>
       <c r="I46" s="20"/>
       <c r="J46" s="20"/>
       <c r="K46" s="20"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="18"/>
-      <c r="B47" s="19" t="str">
-        <f>B38</f>
-        <v>-for side wall of stand tap</v>
-      </c>
-      <c r="C47" s="20">
-        <f>C38</f>
-        <v>3</v>
-      </c>
-      <c r="D47" s="21">
-        <f>D38</f>
-        <v>1.32</v>
-      </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21">
-        <f>F38</f>
-        <v>0.6</v>
-      </c>
-      <c r="G47" s="21">
-        <f>PRODUCT(C47:F47)</f>
-        <v>2.3759999999999999</v>
-      </c>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19" t="str">
-        <f>B39</f>
-        <v>-for stand tap</v>
-      </c>
-      <c r="C48" s="20">
-        <f>C39</f>
-        <v>3</v>
-      </c>
-      <c r="D48" s="21">
-        <f>D39</f>
-        <v>0.35</v>
-      </c>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21">
-        <f>F39</f>
-        <v>1.2</v>
-      </c>
-      <c r="G48" s="21">
-        <f>PRODUCT(C48:F48)</f>
-        <v>1.2599999999999998</v>
-      </c>
+    <row r="47" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="8"/>
+    </row>
+    <row r="48" spans="1:25" ht="168" x14ac:dyDescent="0.25">
+      <c r="A48" s="18">
+        <v>8</v>
+      </c>
+      <c r="B48" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
       <c r="H48" s="20"/>
       <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
+      <c r="J48" s="17"/>
       <c r="K48" s="20"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="10"/>
+      <c r="X48" s="10"/>
+      <c r="Y48" s="10"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="18"/>
-      <c r="B49" s="19"/>
+      <c r="B49" s="19" t="s">
+        <v>34</v>
+      </c>
       <c r="C49" s="20">
-        <f>C40</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" s="21">
-        <f>D40</f>
-        <v>0.46</v>
-      </c>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21">
-        <f>F40</f>
-        <v>0.6</v>
+        <v>200</v>
+      </c>
+      <c r="E49" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="F49" s="20">
+        <v>0.45</v>
       </c>
       <c r="G49" s="21">
         <f>PRODUCT(C49:F49)</f>
-        <v>0.82800000000000007</v>
+        <v>13.5</v>
       </c>
       <c r="H49" s="20"/>
       <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
+      <c r="J49" s="17"/>
       <c r="K49" s="20"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="18"/>
       <c r="B50" s="19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C50" s="20">
-        <f>C15</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="21">
-        <v>1.68</v>
-      </c>
-      <c r="E50" s="21">
-        <v>1.68</v>
-      </c>
-      <c r="F50" s="21"/>
+        <v>150</v>
+      </c>
+      <c r="E50" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="F50" s="20">
+        <v>0.45</v>
+      </c>
       <c r="G50" s="21">
         <f>PRODUCT(C50:F50)</f>
-        <v>8.4672000000000001</v>
+        <v>20.25</v>
       </c>
       <c r="H50" s="20"/>
       <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
+      <c r="J50" s="17"/>
       <c r="K50" s="20"/>
     </row>
-    <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
-      <c r="B51" s="13" t="s">
-        <v>16</v>
+      <c r="B51" s="42" t="s">
+        <v>23</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="1"/>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
-      <c r="G51" s="2">
-        <f>SUM(G46:G50)</f>
-        <v>21.571199999999997</v>
+      <c r="G51" s="43">
+        <f>SUM(G49:G50)</f>
+        <v>33.75</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="I51" s="2">
-        <f>28609.6/100</f>
-        <v>286.096</v>
-      </c>
-      <c r="J51" s="17">
+        <f>1.15*748.9</f>
+        <v>861.2349999999999</v>
+      </c>
+      <c r="J51" s="43">
         <f>G51*I51</f>
-        <v>6171.434035199999</v>
+        <v>29066.681249999998</v>
       </c>
       <c r="K51" s="15"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="9"/>
+      <c r="X51" s="9"/>
+      <c r="Y51" s="9"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="18"/>
-      <c r="B52" s="19" t="s">
-        <v>47</v>
-      </c>
+      <c r="B52" s="19"/>
       <c r="C52" s="20"/>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
@@ -2304,15 +2315,16 @@
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
-      <c r="J52" s="17">
-        <f>0.13*G51*6809.6/100</f>
-        <v>190.958616576</v>
-      </c>
+      <c r="J52" s="17"/>
       <c r="K52" s="20"/>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A53" s="18"/>
-      <c r="B53" s="20"/>
+    <row r="53" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="18">
+        <v>9</v>
+      </c>
+      <c r="B53" s="41" t="s">
+        <v>64</v>
+      </c>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
@@ -2322,90 +2334,97 @@
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
       <c r="K53" s="20"/>
-    </row>
-    <row r="54" spans="1:25" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="18">
-        <v>7</v>
-      </c>
-      <c r="B54" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A54" s="18"/>
+      <c r="B54" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="20">
+        <f>C50</f>
+        <v>2</v>
+      </c>
+      <c r="D54" s="21">
+        <f>D50</f>
+        <v>150</v>
+      </c>
       <c r="E54" s="20"/>
       <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+      <c r="G54" s="21">
+        <f>PRODUCT(C54:F54)</f>
+        <v>300</v>
+      </c>
       <c r="H54" s="20"/>
       <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
+      <c r="J54" s="17"/>
       <c r="K54" s="20"/>
-      <c r="S54" s="10"/>
-      <c r="T54" s="10"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="18"/>
-      <c r="B55" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="20">
-        <f>C15</f>
-        <v>3</v>
-      </c>
-      <c r="D55" s="21">
-        <v>1.2</v>
-      </c>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="21">
-        <f>PRODUCT(C55:F55)</f>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="20"/>
-    </row>
-    <row r="56" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" s="14"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="43">
-        <f>SUM(G55:G55)</f>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="H56" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I56" s="2">
-        <v>248</v>
-      </c>
-      <c r="J56" s="43">
-        <f>G56*I56</f>
-        <v>892.8</v>
-      </c>
-      <c r="K56" s="15"/>
-      <c r="S56" s="9"/>
-      <c r="T56" s="9"/>
-      <c r="U56" s="9"/>
-      <c r="V56" s="9"/>
-      <c r="W56" s="9"/>
-      <c r="X56" s="9"/>
-      <c r="Y56" s="9"/>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
-      <c r="B57" s="19" t="s">
-        <v>61</v>
+    </row>
+    <row r="55" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="12"/>
+      <c r="B55" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="43">
+        <f>SUM(G54:G54)</f>
+        <v>300</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="2">
+        <f>1.15*4308.15/1000</f>
+        <v>4.9543724999999998</v>
+      </c>
+      <c r="J55" s="43">
+        <f>G55*I55</f>
+        <v>1486.3117499999998</v>
+      </c>
+      <c r="K55" s="15"/>
+      <c r="S55" s="9"/>
+      <c r="T55" s="9"/>
+      <c r="U55" s="9"/>
+      <c r="V55" s="9"/>
+      <c r="W55" s="9"/>
+      <c r="X55" s="9"/>
+      <c r="Y55" s="9"/>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A56" s="18"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
+      <c r="X56" s="10"/>
+      <c r="Y56" s="10"/>
+    </row>
+    <row r="57" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="18">
+        <v>10</v>
+      </c>
+      <c r="B57" s="41" t="s">
+        <v>59</v>
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
@@ -2414,10 +2433,7 @@
       <c r="G57" s="20"/>
       <c r="H57" s="20"/>
       <c r="I57" s="20"/>
-      <c r="J57" s="17">
-        <f>0.13*J56</f>
-        <v>116.06399999999999</v>
-      </c>
+      <c r="J57" s="20"/>
       <c r="K57" s="20"/>
       <c r="S57" s="10"/>
       <c r="T57" s="10"/>
@@ -2429,41 +2445,63 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
-      <c r="B58" s="41"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
+      <c r="B58" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="20">
+        <v>1</v>
+      </c>
+      <c r="D58" s="21">
+        <f>D49</f>
+        <v>200</v>
+      </c>
       <c r="E58" s="20"/>
       <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
+      <c r="G58" s="21">
+        <f>PRODUCT(C58:F58)</f>
+        <v>200</v>
+      </c>
       <c r="H58" s="20"/>
       <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
+      <c r="J58" s="17"/>
       <c r="K58" s="20"/>
     </row>
-    <row r="59" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="8"/>
-    </row>
-    <row r="60" spans="1:25" ht="168" x14ac:dyDescent="0.25">
-      <c r="A60" s="18">
-        <v>8</v>
-      </c>
-      <c r="B60" s="41" t="s">
-        <v>72</v>
-      </c>
+    <row r="59" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="12"/>
+      <c r="B59" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" s="14"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="43">
+        <f>SUM(G58:G58)</f>
+        <v>200</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="2">
+        <f>1.15*5319.5/1000</f>
+        <v>6.117424999999999</v>
+      </c>
+      <c r="J59" s="43">
+        <f>G59*I59</f>
+        <v>1223.4849999999999</v>
+      </c>
+      <c r="K59" s="15"/>
+      <c r="S59" s="9"/>
+      <c r="T59" s="9"/>
+      <c r="U59" s="9"/>
+      <c r="V59" s="9"/>
+      <c r="W59" s="9"/>
+      <c r="X59" s="9"/>
+      <c r="Y59" s="9"/>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A60" s="18"/>
+      <c r="B60" s="41"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
@@ -2471,7 +2509,7 @@
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
       <c r="I60" s="20"/>
-      <c r="J60" s="17"/>
+      <c r="J60" s="20"/>
       <c r="K60" s="20"/>
       <c r="S60" s="10"/>
       <c r="T60" s="10"/>
@@ -2481,82 +2519,93 @@
       <c r="X60" s="10"/>
       <c r="Y60" s="10"/>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
-      <c r="B61" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C61" s="20">
-        <v>1</v>
-      </c>
-      <c r="D61" s="21">
-        <v>200</v>
-      </c>
-      <c r="E61" s="20">
-        <v>0.15</v>
-      </c>
-      <c r="F61" s="20">
-        <v>0.45</v>
-      </c>
-      <c r="G61" s="21">
-        <f>PRODUCT(C61:F61)</f>
-        <v>13.5</v>
-      </c>
+    <row r="61" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="18">
+        <v>11</v>
+      </c>
+      <c r="B61" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="20"/>
+      <c r="D61" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="20"/>
       <c r="H61" s="20"/>
       <c r="I61" s="20"/>
       <c r="J61" s="17"/>
       <c r="K61" s="20"/>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
-      <c r="B62" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" s="20">
+      <c r="B62" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="27">
+        <f>C54</f>
         <v>2</v>
       </c>
-      <c r="D62" s="21">
+      <c r="D62" s="36">
+        <f>D54</f>
         <v>150</v>
       </c>
-      <c r="E62" s="20">
-        <v>0.15</v>
-      </c>
-      <c r="F62" s="20">
-        <v>0.45</v>
-      </c>
-      <c r="G62" s="21">
-        <f>PRODUCT(C62:F62)</f>
-        <v>20.25</v>
-      </c>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="20"/>
-    </row>
-    <row r="63" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
-      <c r="B63" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C63" s="14"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="43">
-        <f>SUM(G61:G62)</f>
-        <v>33.75</v>
-      </c>
-      <c r="H63" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I63" s="2">
-        <v>748.9</v>
-      </c>
-      <c r="J63" s="43">
-        <f>G63*I63</f>
-        <v>25275.375</v>
-      </c>
-      <c r="K63" s="15"/>
+      <c r="E62" s="27">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="F62" s="27">
+        <f>C62*D62*E62</f>
+        <v>40.5</v>
+      </c>
+      <c r="G62" s="36">
+        <f>F62</f>
+        <v>40.5</v>
+      </c>
+      <c r="H62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="27"/>
+      <c r="S62" s="9"/>
+      <c r="T62" s="9"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="9"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="9"/>
+    </row>
+    <row r="63" spans="1:25" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="18"/>
+      <c r="B63" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="27">
+        <f>C58</f>
+        <v>1</v>
+      </c>
+      <c r="D63" s="36">
+        <f>D58</f>
+        <v>200</v>
+      </c>
+      <c r="E63" s="27">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="F63" s="27">
+        <f>C63*D63*E63</f>
+        <v>67.600000000000009</v>
+      </c>
+      <c r="G63" s="36">
+        <f>F63</f>
+        <v>67.600000000000009</v>
+      </c>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="27"/>
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
       <c r="U63" s="9"/>
@@ -2565,26 +2614,34 @@
       <c r="X63" s="9"/>
       <c r="Y63" s="9"/>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A64" s="18"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="20"/>
-    </row>
-    <row r="65" spans="1:25" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="18">
-        <v>9</v>
-      </c>
-      <c r="B65" s="41" t="s">
-        <v>75</v>
-      </c>
+    <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="12"/>
+      <c r="B64" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="14"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="2">
+        <f>SUM(G62:G63)</f>
+        <v>108.10000000000001</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="2">
+        <v>287</v>
+      </c>
+      <c r="J64" s="17">
+        <f>G64*I64</f>
+        <v>31024.7</v>
+      </c>
+      <c r="K64" s="15"/>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A65" s="18"/>
+      <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
@@ -2594,98 +2651,88 @@
       <c r="I65" s="20"/>
       <c r="J65" s="20"/>
       <c r="K65" s="20"/>
-      <c r="S65" s="10"/>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
-      <c r="V65" s="10"/>
-      <c r="W65" s="10"/>
-      <c r="X65" s="10"/>
-      <c r="Y65" s="10"/>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
-      <c r="B66" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C66" s="20">
-        <f>C62</f>
-        <v>2</v>
-      </c>
-      <c r="D66" s="21">
-        <f>D62</f>
-        <v>150</v>
-      </c>
+      <c r="A66" s="18">
+        <v>12</v>
+      </c>
+      <c r="B66" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="20"/>
-      <c r="G66" s="21">
-        <f>PRODUCT(C66:F66)</f>
-        <v>300</v>
-      </c>
+      <c r="G66" s="20"/>
       <c r="H66" s="20"/>
       <c r="I66" s="20"/>
-      <c r="J66" s="17"/>
+      <c r="J66" s="20"/>
       <c r="K66" s="20"/>
-    </row>
-    <row r="67" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="12"/>
-      <c r="B67" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C67" s="14"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="43">
-        <f>SUM(G66:G66)</f>
-        <v>300</v>
-      </c>
-      <c r="H67" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I67" s="2">
-        <f>4308.15/1000</f>
-        <v>4.3081499999999995</v>
-      </c>
-      <c r="J67" s="43">
-        <f>G67*I67</f>
-        <v>1292.4449999999999</v>
-      </c>
-      <c r="K67" s="15"/>
-      <c r="S67" s="9"/>
-      <c r="T67" s="9"/>
-      <c r="U67" s="9"/>
-      <c r="V67" s="9"/>
-      <c r="W67" s="9"/>
-      <c r="X67" s="9"/>
-      <c r="Y67" s="9"/>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A68" s="18"/>
-      <c r="B68" s="41"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
-      <c r="K68" s="20"/>
-      <c r="S68" s="10"/>
-      <c r="T68" s="10"/>
-      <c r="U68" s="10"/>
-      <c r="V68" s="10"/>
-      <c r="W68" s="10"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="10"/>
-    </row>
-    <row r="69" spans="1:25" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="18">
+      <c r="S66" s="10"/>
+      <c r="T66" s="10"/>
+      <c r="U66" s="10"/>
+      <c r="V66" s="10"/>
+      <c r="W66" s="10"/>
+      <c r="X66" s="10"/>
+      <c r="Y66" s="10"/>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A67" s="18"/>
+      <c r="B67" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" s="20">
+        <v>2</v>
+      </c>
+      <c r="D67" s="21">
+        <v>5000</v>
+      </c>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="21">
+        <f>PRODUCT(C67:F67)</f>
+        <v>10000</v>
+      </c>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="20"/>
+    </row>
+    <row r="68" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="12"/>
+      <c r="B68" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="14"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="43">
+        <f>SUM(G67:G67)</f>
+        <v>10000</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I68" s="2">
         <v>10</v>
       </c>
-      <c r="B69" s="41" t="s">
-        <v>70</v>
-      </c>
+      <c r="J68" s="43">
+        <f>G68*I68</f>
+        <v>100000</v>
+      </c>
+      <c r="K68" s="15"/>
+      <c r="S68" s="9"/>
+      <c r="T68" s="9"/>
+      <c r="U68" s="9"/>
+      <c r="V68" s="9"/>
+      <c r="W68" s="9"/>
+      <c r="X68" s="9"/>
+      <c r="Y68" s="9"/>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A69" s="18"/>
+      <c r="B69" s="41"/>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
@@ -2695,141 +2742,124 @@
       <c r="I69" s="20"/>
       <c r="J69" s="20"/>
       <c r="K69" s="20"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
-      <c r="V69" s="10"/>
-      <c r="W69" s="10"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="10"/>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A70" s="18"/>
-      <c r="B70" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C70" s="20">
-        <v>1</v>
-      </c>
-      <c r="D70" s="21">
-        <f>D61</f>
-        <v>200</v>
-      </c>
+      <c r="A70" s="18">
+        <v>13</v>
+      </c>
+      <c r="B70" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
       <c r="E70" s="20"/>
       <c r="F70" s="20"/>
-      <c r="G70" s="21">
-        <f>PRODUCT(C70:F70)</f>
-        <v>200</v>
-      </c>
+      <c r="G70" s="20"/>
       <c r="H70" s="20"/>
       <c r="I70" s="20"/>
-      <c r="J70" s="17"/>
+      <c r="J70" s="20"/>
       <c r="K70" s="20"/>
-    </row>
-    <row r="71" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="12"/>
-      <c r="B71" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C71" s="14"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="43">
-        <f>SUM(G70:G70)</f>
-        <v>200</v>
-      </c>
-      <c r="H71" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I71" s="2">
-        <f>5319.5/1000</f>
-        <v>5.3194999999999997</v>
-      </c>
-      <c r="J71" s="43">
-        <f>G71*I71</f>
-        <v>1063.8999999999999</v>
-      </c>
-      <c r="K71" s="15"/>
-      <c r="S71" s="9"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A72" s="18"/>
-      <c r="B72" s="41"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
-      <c r="K72" s="20"/>
-      <c r="S72" s="10"/>
-      <c r="T72" s="10"/>
-      <c r="U72" s="10"/>
-      <c r="V72" s="10"/>
-      <c r="W72" s="10"/>
-      <c r="X72" s="10"/>
-      <c r="Y72" s="10"/>
-    </row>
-    <row r="73" spans="1:25" ht="45" x14ac:dyDescent="0.25">
-      <c r="A73" s="18">
-        <v>11</v>
-      </c>
-      <c r="B73" s="45" t="s">
-        <v>30</v>
-      </c>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="10"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="10"/>
+      <c r="X70" s="10"/>
+      <c r="Y70" s="10"/>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A71" s="18"/>
+      <c r="B71" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="20">
+        <v>1</v>
+      </c>
+      <c r="D71" s="21"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="21">
+        <f>PRODUCT(C71:F71)</f>
+        <v>1</v>
+      </c>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="20"/>
+    </row>
+    <row r="72" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="12"/>
+      <c r="B72" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="14"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="43">
+        <f>SUM(G71:G71)</f>
+        <v>1</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="I72" s="2">
+        <v>30930</v>
+      </c>
+      <c r="J72" s="43">
+        <f>G72*I72</f>
+        <v>30930</v>
+      </c>
+      <c r="K72" s="15"/>
+      <c r="S72" s="9"/>
+      <c r="T72" s="9"/>
+      <c r="U72" s="9"/>
+      <c r="V72" s="9"/>
+      <c r="W72" s="9"/>
+      <c r="X72" s="9"/>
+      <c r="Y72" s="9"/>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A73" s="18"/>
+      <c r="B73" s="41"/>
       <c r="C73" s="20"/>
-      <c r="D73" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E73" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F73" s="26" t="s">
-        <v>32</v>
-      </c>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
       <c r="I73" s="20"/>
-      <c r="J73" s="17"/>
+      <c r="J73" s="20"/>
       <c r="K73" s="20"/>
     </row>
     <row r="74" spans="1:25" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="18"/>
-      <c r="B74" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="C74" s="27">
-        <f>C66</f>
-        <v>2</v>
-      </c>
-      <c r="D74" s="36">
-        <f>D66</f>
-        <v>150</v>
-      </c>
-      <c r="E74" s="27">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="F74" s="27">
-        <f>C74*D74*E74</f>
-        <v>40.5</v>
-      </c>
-      <c r="G74" s="36">
-        <f>F74</f>
-        <v>40.5</v>
-      </c>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="27"/>
+      <c r="A74" s="12">
+        <v>14</v>
+      </c>
+      <c r="B74" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="14">
+        <v>1</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="43">
+        <f>PRODUCT(C74:F74)</f>
+        <v>1</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I74" s="2">
+        <v>7000</v>
+      </c>
+      <c r="J74" s="43">
+        <f>G74*I74</f>
+        <v>7000</v>
+      </c>
+      <c r="K74" s="15"/>
       <c r="S74" s="9"/>
       <c r="T74" s="9"/>
       <c r="U74" s="9"/>
@@ -2838,543 +2868,113 @@
       <c r="X74" s="9"/>
       <c r="Y74" s="9"/>
     </row>
-    <row r="75" spans="1:25" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="C75" s="27">
-        <f>C70</f>
+      <c r="B75" s="41"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="20"/>
+    </row>
+    <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="12">
+        <v>15</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="14">
         <v>1</v>
       </c>
-      <c r="D75" s="36">
-        <f>D70</f>
-        <v>200</v>
-      </c>
-      <c r="E75" s="27">
-        <v>0.33800000000000002</v>
-      </c>
-      <c r="F75" s="27">
-        <f>C75*D75*E75</f>
-        <v>67.600000000000009</v>
-      </c>
-      <c r="G75" s="36">
-        <f>F75</f>
-        <v>67.600000000000009</v>
-      </c>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="27"/>
-      <c r="S75" s="9"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-    </row>
-    <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="12"/>
-      <c r="B76" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" s="14"/>
       <c r="D76" s="1"/>
       <c r="E76" s="15"/>
       <c r="F76" s="15"/>
-      <c r="G76" s="2">
-        <f>SUM(G74:G75)</f>
-        <v>108.10000000000001</v>
+      <c r="G76" s="16">
+        <f>PRODUCT(C76:F76)</f>
+        <v>1</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I76" s="2">
-        <v>287</v>
-      </c>
-      <c r="J76" s="17">
+        <v>500</v>
+      </c>
+      <c r="J76" s="16">
         <f>G76*I76</f>
-        <v>31024.7</v>
+        <v>500</v>
       </c>
       <c r="K76" s="15"/>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A77" s="18"/>
-      <c r="B77" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C77" s="20"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
-      <c r="J77" s="17">
-        <f>0.13*J76</f>
-        <v>4033.2110000000002</v>
-      </c>
-      <c r="K77" s="20"/>
+      <c r="A77" s="12"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="15"/>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A78" s="18"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-      <c r="J78" s="20"/>
-      <c r="K78" s="20"/>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A79" s="18">
-        <v>12</v>
-      </c>
-      <c r="B79" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
-      <c r="J79" s="20"/>
-      <c r="K79" s="20"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
-      <c r="V79" s="10"/>
-      <c r="W79" s="10"/>
-      <c r="X79" s="10"/>
-      <c r="Y79" s="10"/>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A80" s="18"/>
-      <c r="B80" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C80" s="20">
-        <v>2</v>
-      </c>
-      <c r="D80" s="21">
-        <v>5000</v>
-      </c>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="21">
-        <f>PRODUCT(C80:F80)</f>
-        <v>10000</v>
-      </c>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="20"/>
-    </row>
-    <row r="81" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="12"/>
-      <c r="B81" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C81" s="14"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="43">
-        <f>SUM(G80:G80)</f>
-        <v>10000</v>
-      </c>
-      <c r="H81" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="I81" s="2">
-        <v>10</v>
-      </c>
-      <c r="J81" s="43">
-        <f>G81*I81</f>
-        <v>100000</v>
-      </c>
-      <c r="K81" s="15"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
-      <c r="V81" s="9"/>
-      <c r="W81" s="9"/>
-      <c r="X81" s="9"/>
-      <c r="Y81" s="9"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A82" s="18"/>
-      <c r="B82" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
-      <c r="J82" s="17">
-        <f>0.13*J81</f>
-        <v>13000</v>
-      </c>
-      <c r="K82" s="20"/>
-      <c r="S82" s="10"/>
-      <c r="T82" s="10"/>
-      <c r="U82" s="10"/>
-      <c r="V82" s="10"/>
-      <c r="W82" s="10"/>
-      <c r="X82" s="10"/>
-      <c r="Y82" s="10"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A83" s="18"/>
-      <c r="B83" s="41"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="20"/>
-      <c r="K83" s="20"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A84" s="18">
-        <v>13</v>
-      </c>
-      <c r="B84" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-      <c r="J84" s="20"/>
-      <c r="K84" s="20"/>
-      <c r="S84" s="10"/>
-      <c r="T84" s="10"/>
-      <c r="U84" s="10"/>
-      <c r="V84" s="10"/>
-      <c r="W84" s="10"/>
-      <c r="X84" s="10"/>
-      <c r="Y84" s="10"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A85" s="18"/>
-      <c r="B85" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" s="20">
-        <v>1</v>
-      </c>
-      <c r="D85" s="21"/>
-      <c r="E85" s="20"/>
-      <c r="F85" s="20"/>
-      <c r="G85" s="21">
-        <f>PRODUCT(C85:F85)</f>
-        <v>1</v>
-      </c>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-      <c r="J85" s="17"/>
-      <c r="K85" s="20"/>
-    </row>
-    <row r="86" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="12"/>
-      <c r="B86" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C86" s="14"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="15"/>
-      <c r="F86" s="15"/>
-      <c r="G86" s="43">
-        <f>SUM(G85:G85)</f>
-        <v>1</v>
-      </c>
-      <c r="H86" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="I86" s="2">
-        <v>30930</v>
-      </c>
-      <c r="J86" s="43">
-        <f>G86*I86</f>
-        <v>30930</v>
-      </c>
-      <c r="K86" s="15"/>
-      <c r="S86" s="9"/>
-      <c r="T86" s="9"/>
-      <c r="U86" s="9"/>
-      <c r="V86" s="9"/>
-      <c r="W86" s="9"/>
-      <c r="X86" s="9"/>
-      <c r="Y86" s="9"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A87" s="18"/>
-      <c r="B87" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
-      <c r="J87" s="17">
-        <f>0.13*J86</f>
-        <v>4020.9</v>
-      </c>
-      <c r="K87" s="20"/>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
-      <c r="U87" s="10"/>
-      <c r="V87" s="10"/>
-      <c r="W87" s="10"/>
-      <c r="X87" s="10"/>
-      <c r="Y87" s="10"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A88" s="18"/>
-      <c r="B88" s="41"/>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="20"/>
-      <c r="K88" s="20"/>
-    </row>
-    <row r="89" spans="1:25" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="12">
-        <v>14</v>
-      </c>
-      <c r="B89" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C89" s="14">
-        <v>1</v>
-      </c>
-      <c r="D89" s="1"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="43">
-        <f>PRODUCT(C89:F89)</f>
-        <v>1</v>
-      </c>
-      <c r="H89" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I89" s="2">
-        <v>7000</v>
-      </c>
-      <c r="J89" s="43">
-        <f>G89*I89</f>
-        <v>7000</v>
-      </c>
-      <c r="K89" s="15"/>
-      <c r="S89" s="9"/>
-      <c r="T89" s="9"/>
-      <c r="U89" s="9"/>
-      <c r="V89" s="9"/>
-      <c r="W89" s="9"/>
-      <c r="X89" s="9"/>
-      <c r="Y89" s="9"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A90" s="18"/>
-      <c r="B90" s="41"/>
-      <c r="C90" s="20"/>
-      <c r="D90" s="20"/>
-      <c r="E90" s="20"/>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20"/>
-      <c r="I90" s="20"/>
-      <c r="J90" s="20"/>
-      <c r="K90" s="20"/>
-    </row>
-    <row r="91" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="12">
-        <v>15</v>
-      </c>
-      <c r="B91" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" s="14">
-        <v>1</v>
-      </c>
-      <c r="D91" s="1"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="16">
-        <f>PRODUCT(C91:F91)</f>
-        <v>1</v>
-      </c>
-      <c r="H91" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I91" s="2">
-        <v>500</v>
-      </c>
-      <c r="J91" s="16">
-        <f>G91*I91</f>
-        <v>500</v>
-      </c>
-      <c r="K91" s="15"/>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A92" s="12"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="16"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="17"/>
-      <c r="K92" s="15"/>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A93" s="30"/>
-      <c r="B93" s="31" t="s">
+      <c r="A78" s="30"/>
+      <c r="B78" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C93" s="32"/>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="33"/>
-      <c r="G93" s="17"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-      <c r="J93" s="17">
-        <f>SUM(J9:J91)</f>
-        <v>280111.34405766404</v>
-      </c>
-      <c r="K93" s="34"/>
-      <c r="S93" s="10"/>
-      <c r="T93" s="10"/>
-      <c r="U93" s="10"/>
-      <c r="V93" s="10"/>
-      <c r="W93" s="10"/>
-      <c r="X93" s="10"/>
-      <c r="Y93" s="10"/>
-    </row>
-    <row r="95" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="35"/>
-      <c r="B95" s="27" t="s">
+      <c r="C78" s="32"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="33"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17">
+        <f>SUM(J9:J76)</f>
+        <v>266750.84614749998</v>
+      </c>
+      <c r="K78" s="34"/>
+      <c r="S78" s="10"/>
+      <c r="T78" s="10"/>
+      <c r="U78" s="10"/>
+      <c r="V78" s="10"/>
+      <c r="W78" s="10"/>
+      <c r="X78" s="10"/>
+      <c r="Y78" s="10"/>
+    </row>
+    <row r="80" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="35"/>
+      <c r="B80" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C95" s="55">
-        <f>J93</f>
-        <v>280111.34405766404</v>
-      </c>
-      <c r="D95" s="56"/>
-      <c r="E95" s="36">
-        <v>100</v>
-      </c>
-      <c r="F95" s="35"/>
-      <c r="G95" s="37"/>
-      <c r="H95" s="35"/>
-      <c r="I95" s="38"/>
-      <c r="J95" s="39"/>
-      <c r="K95" s="40"/>
-      <c r="S95" s="9"/>
-      <c r="T95" s="9"/>
-      <c r="U95" s="9"/>
-      <c r="V95" s="9"/>
-      <c r="W95" s="9"/>
-      <c r="X95" s="9"/>
-      <c r="Y95" s="9"/>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B96" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C96" s="57">
-        <v>250000</v>
-      </c>
-      <c r="D96" s="58"/>
-      <c r="E96" s="36"/>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B97" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C97" s="57">
-        <f>C96-C99-C100</f>
-        <v>237500</v>
-      </c>
-      <c r="D97" s="58"/>
-      <c r="E97" s="36">
-        <f>C97/C95*100</f>
-        <v>84.787712114618245</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B98" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C98" s="59">
-        <f>C95-C97</f>
-        <v>42611.344057664042</v>
-      </c>
-      <c r="D98" s="59"/>
-      <c r="E98" s="36">
-        <f>100-E97</f>
-        <v>15.212287885381755</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B99" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C99" s="55">
-        <f>C96*0.03</f>
-        <v>7500</v>
-      </c>
-      <c r="D99" s="56"/>
-      <c r="E99" s="36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B100" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C100" s="55">
-        <f>C96*0.02</f>
-        <v>5000</v>
-      </c>
-      <c r="D100" s="56"/>
-      <c r="E100" s="36">
-        <v>2</v>
-      </c>
+      <c r="C80" s="47">
+        <f>J78</f>
+        <v>266750.84614749998</v>
+      </c>
+      <c r="D80" s="48"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="35"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="35"/>
+      <c r="I80" s="38"/>
+      <c r="J80" s="39"/>
+      <c r="K80" s="40"/>
+      <c r="S80" s="9"/>
+      <c r="T80" s="9"/>
+      <c r="U80" s="9"/>
+      <c r="V80" s="9"/>
+      <c r="W80" s="9"/>
+      <c r="X80" s="9"/>
+      <c r="Y80" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
+  <mergeCells count="10">
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -3384,6 +2984,7 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C80:D80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -3412,27 +3013,27 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
